--- a/src/strendcat_biocatalysis/schema/comparison.xlsx
+++ b/src/strendcat_biocatalysis/schema/comparison.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\StrenDCAT-Biocatalysis\src\strendcat_biocatalysis\schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D2A79CB-1522-404A-9428-7F49575A1241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326D0F3D-27FD-41BB-ACCF-409DEB7F5233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DE9B59C-CD8C-42BC-9FD3-3BA2E451A179}"/>
   </bookViews>
   <sheets>
     <sheet name="test" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="592">
   <si>
     <t>file</t>
   </si>
@@ -1797,7 +1808,10 @@
     <t>Volumetric value of the vessel.</t>
   </si>
   <si>
-    <t>Maps to STRENDCAT Object</t>
+    <t>Direct Mapping?</t>
+  </si>
+  <si>
+    <t>Semantic Mapping to STRENDCAT Object</t>
   </si>
 </sst>
 </file>
@@ -2670,24 +2684,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21EF845A-581D-4E43-B9D4-125E9A870B43}">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:M197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.42578125" customWidth="1"/>
     <col min="2" max="2" width="32.140625" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="2" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="4"/>
-    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" customWidth="1"/>
+    <col min="8" max="8" width="31.42578125" customWidth="1"/>
     <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="1.5703125" customWidth="1"/>
     <col min="11" max="11" width="34.7109375" customWidth="1"/>
     <col min="12" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2722,8 +2736,11 @@
       <c r="L1" s="2" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M1" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2754,8 +2771,12 @@
       <c r="K2" s="1" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L2" t="e">
+        <f>_xlfn.XMATCH(I2,$C$2:$C$197)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2786,8 +2807,12 @@
       <c r="K3" s="1" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L3" t="e">
+        <f t="shared" ref="L3:L35" si="0">_xlfn.XMATCH(I3,$C$2:$C$197)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2818,8 +2843,12 @@
       <c r="K4" s="1" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L4" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2850,8 +2879,12 @@
       <c r="K5" s="1" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L5" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2882,8 +2915,12 @@
       <c r="K6" s="1" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L6" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2914,8 +2951,12 @@
       <c r="K7" s="1" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L7" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2946,8 +2987,12 @@
       <c r="K8" s="1" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L8" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2978,8 +3023,12 @@
       <c r="K9" s="1" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L9" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -3010,8 +3059,12 @@
       <c r="K10" s="1" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L10" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -3042,8 +3095,12 @@
       <c r="K11" s="1" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L11" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -3074,8 +3131,12 @@
       <c r="K12" s="1" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -3106,8 +3167,12 @@
       <c r="K13" s="1" t="s">
         <v>531</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L13" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -3138,8 +3203,12 @@
       <c r="K14" s="1" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L14" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -3170,8 +3239,12 @@
       <c r="K15" s="1" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L15" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -3202,8 +3275,12 @@
       <c r="K16" s="1" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L16" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -3234,8 +3311,12 @@
       <c r="K17" s="1" t="s">
         <v>543</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L17" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -3266,8 +3347,12 @@
       <c r="K18" s="1" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L18" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3298,8 +3383,12 @@
       <c r="K19" s="1" t="s">
         <v>549</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L19" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -3330,8 +3419,12 @@
       <c r="K20" s="1" t="s">
         <v>551</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L20" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -3362,8 +3455,12 @@
       <c r="K21" s="1" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L21" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -3394,8 +3491,12 @@
       <c r="K22" s="1" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L22" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -3426,8 +3527,12 @@
       <c r="K23" s="1" t="s">
         <v>559</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L23" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -3458,8 +3563,12 @@
       <c r="K24" s="1" t="s">
         <v>561</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L24" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -3490,8 +3599,12 @@
       <c r="K25" s="1" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L25" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -3522,8 +3635,12 @@
       <c r="K26" s="1" t="s">
         <v>540</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L26" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -3554,8 +3671,12 @@
       <c r="K27" s="1" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L27" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -3586,8 +3707,12 @@
       <c r="K28" s="1" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L28" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -3618,8 +3743,12 @@
       <c r="K29" s="1" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L29" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -3650,8 +3779,12 @@
       <c r="K30" s="1" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L30" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -3682,8 +3815,12 @@
       <c r="K31" s="1" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L31" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -3714,8 +3851,12 @@
       <c r="K32" s="1" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L32" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -3746,8 +3887,12 @@
       <c r="K33" s="1" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L33" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -3778,8 +3923,12 @@
       <c r="K34" s="1" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L34" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -3810,8 +3959,12 @@
       <c r="K35" s="1" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L35" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -3828,7 +3981,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -3845,7 +3998,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -3862,7 +4015,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -3879,7 +4032,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -3896,7 +4049,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -3913,7 +4066,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -3930,7 +4083,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -3947,7 +4100,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -3964,7 +4117,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -3978,7 +4131,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -3992,7 +4145,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -4006,7 +4159,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -4020,7 +4173,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -4034,7 +4187,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -4048,7 +4201,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -4062,7 +4215,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -4076,7 +4229,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -4090,7 +4243,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -4104,7 +4257,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -4118,7 +4271,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -4132,7 +4285,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -4146,7 +4299,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -4160,7 +4313,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -4174,7 +4327,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -4188,7 +4341,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -4202,7 +4355,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -4216,7 +4369,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -4230,7 +4383,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -4244,7 +4397,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -4258,7 +4411,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -4272,7 +4425,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -4286,7 +4439,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -4300,7 +4453,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -4314,7 +4467,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -4328,7 +4481,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -4342,7 +4495,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -4356,7 +4509,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -4370,7 +4523,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -4384,7 +4537,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -4398,7 +4551,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -4412,7 +4565,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -4426,7 +4579,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -4440,7 +4593,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -4454,7 +4607,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -4468,7 +4621,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -4482,7 +4635,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -4496,7 +4649,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -4510,7 +4663,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -4524,7 +4677,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -4538,7 +4691,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -4552,7 +4705,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -4566,7 +4719,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -4580,7 +4733,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -4594,7 +4747,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -4608,7 +4761,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -4622,7 +4775,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>5</v>
       </c>
@@ -4636,7 +4789,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>5</v>
       </c>
@@ -4650,7 +4803,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>5</v>
       </c>
@@ -4664,7 +4817,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>5</v>
       </c>
@@ -4678,7 +4831,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -4692,7 +4845,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -4706,7 +4859,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>5</v>
       </c>
@@ -4720,7 +4873,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>5</v>
       </c>
@@ -4734,7 +4887,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>5</v>
       </c>
@@ -4748,7 +4901,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>5</v>
       </c>
@@ -4762,7 +4915,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>5</v>
       </c>
@@ -4776,7 +4929,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>5</v>
       </c>
@@ -4790,7 +4943,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>5</v>
       </c>
@@ -4804,7 +4957,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>5</v>
       </c>
@@ -4818,7 +4971,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>5</v>
       </c>
@@ -4832,7 +4985,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>5</v>
       </c>
@@ -4846,7 +4999,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>5</v>
       </c>
@@ -4860,7 +5013,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>5</v>
       </c>
@@ -4874,7 +5027,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -4888,7 +5041,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>5</v>
       </c>
@@ -4902,7 +5055,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>5</v>
       </c>
@@ -4916,7 +5069,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>5</v>
       </c>
@@ -4930,7 +5083,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>5</v>
       </c>
@@ -4944,7 +5097,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>5</v>
       </c>
@@ -4958,7 +5111,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>5</v>
       </c>
@@ -4972,7 +5125,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>5</v>
       </c>
@@ -4986,7 +5139,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>5</v>
       </c>
@@ -5000,7 +5153,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>5</v>
       </c>
@@ -5014,7 +5167,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>5</v>
       </c>
@@ -5028,7 +5181,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>5</v>
       </c>
@@ -5042,7 +5195,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>5</v>
       </c>
@@ -5056,7 +5209,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>5</v>
       </c>
@@ -5070,7 +5223,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -5084,7 +5237,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>5</v>
       </c>
@@ -5098,7 +5251,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>5</v>
       </c>
@@ -5112,7 +5265,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>5</v>
       </c>
@@ -5126,7 +5279,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>5</v>
       </c>
@@ -5140,7 +5293,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>5</v>
       </c>
@@ -5154,7 +5307,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>5</v>
       </c>
@@ -5168,7 +5321,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>5</v>
       </c>
@@ -5182,7 +5335,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>5</v>
       </c>
@@ -5196,7 +5349,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>5</v>
       </c>
@@ -5210,7 +5363,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>5</v>
       </c>
@@ -5224,7 +5377,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>5</v>
       </c>
@@ -5238,7 +5391,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>5</v>
       </c>
@@ -5252,7 +5405,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>5</v>
       </c>
@@ -5266,7 +5419,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -5280,7 +5433,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>5</v>
       </c>
@@ -5294,7 +5447,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>5</v>
       </c>
@@ -5308,7 +5461,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>5</v>
       </c>
@@ -5322,7 +5475,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>5</v>
       </c>
@@ -5336,7 +5489,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>5</v>
       </c>
@@ -5350,7 +5503,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>5</v>
       </c>
@@ -5364,7 +5517,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>5</v>
       </c>
@@ -5378,7 +5531,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>5</v>
       </c>
@@ -5392,7 +5545,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>5</v>
       </c>
@@ -5406,7 +5559,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -5420,7 +5573,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>5</v>
       </c>
@@ -5434,7 +5587,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>5</v>
       </c>
@@ -5448,7 +5601,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>5</v>
       </c>
@@ -5462,7 +5615,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -5476,7 +5629,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>5</v>
       </c>
@@ -5490,7 +5643,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>5</v>
       </c>
@@ -5504,7 +5657,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>5</v>
       </c>
@@ -5518,7 +5671,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>5</v>
       </c>
@@ -5532,7 +5685,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>5</v>
       </c>
@@ -5546,7 +5699,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>5</v>
       </c>
@@ -5560,7 +5713,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>5</v>
       </c>
@@ -5574,7 +5727,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>5</v>
       </c>
@@ -5588,7 +5741,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>5</v>
       </c>
@@ -5602,7 +5755,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>5</v>
       </c>
@@ -5616,7 +5769,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>5</v>
       </c>
@@ -5630,7 +5783,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>5</v>
       </c>
@@ -5644,7 +5797,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>5</v>
       </c>
@@ -5658,7 +5811,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>5</v>
       </c>
@@ -5672,7 +5825,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>5</v>
       </c>
@@ -5686,7 +5839,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>5</v>
       </c>
@@ -5700,7 +5853,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>5</v>
       </c>
@@ -5714,7 +5867,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>5</v>
       </c>
@@ -5728,7 +5881,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>5</v>
       </c>
@@ -5742,7 +5895,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>5</v>
       </c>
@@ -5756,7 +5909,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>5</v>
       </c>
@@ -5770,7 +5923,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>5</v>
       </c>
@@ -5784,7 +5937,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>5</v>
       </c>
@@ -5798,7 +5951,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>5</v>
       </c>
@@ -5812,7 +5965,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>5</v>
       </c>
@@ -5826,7 +5979,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>5</v>
       </c>
@@ -5840,7 +5993,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>5</v>
       </c>
@@ -5854,7 +6007,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>5</v>
       </c>
@@ -5868,7 +6021,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>5</v>
       </c>
@@ -5882,7 +6035,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>5</v>
       </c>
@@ -5896,7 +6049,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>5</v>
       </c>
@@ -5910,7 +6063,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>5</v>
       </c>
@@ -5924,7 +6077,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="185" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>5</v>
       </c>
@@ -5938,7 +6091,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>5</v>
       </c>
@@ -5952,7 +6105,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>5</v>
       </c>
@@ -5966,7 +6119,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>5</v>
       </c>
@@ -5980,7 +6133,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>5</v>
       </c>
@@ -5994,7 +6147,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>5</v>
       </c>
@@ -6008,7 +6161,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>5</v>
       </c>
@@ -6022,7 +6175,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>5</v>
       </c>
@@ -6036,7 +6189,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>5</v>
       </c>
@@ -6050,7 +6203,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -6064,7 +6217,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>5</v>
       </c>
@@ -6078,7 +6231,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>5</v>
       </c>
@@ -6092,7 +6245,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>5</v>
       </c>

--- a/src/strendcat_biocatalysis/schema/comparison.xlsx
+++ b/src/strendcat_biocatalysis/schema/comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\StrenDCAT-Biocatalysis\src\strendcat_biocatalysis\schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326D0F3D-27FD-41BB-ACCF-409DEB7F5233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B0EAA9-FBDE-4C11-A5F2-6214135138A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DE9B59C-CD8C-42BC-9FD3-3BA2E451A179}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="631">
   <si>
     <t>file</t>
   </si>
@@ -1811,7 +1811,124 @@
     <t>Direct Mapping?</t>
   </si>
   <si>
-    <t>Semantic Mapping to STRENDCAT Object</t>
+    <t>classes.Complex</t>
+  </si>
+  <si>
+    <t>The Complex object allows the grouping of multiple species using their . This enables the representation of protein-small molecule complexes (e.g., enzyme-substrate complexes) as well as buffer or solvent mixtures (combinations of SmallMolecule species).</t>
+  </si>
+  <si>
+    <t>Ein Complex gruppiert verschiedene Spezies; der Slot beschreibt chemische Komponenten einer Reaktionsmischung.</t>
+  </si>
+  <si>
+    <t>Beide betreffen Komponenten im Kontext eines Komplexes bzw. einer Reaktion, allerdings nicht spezifisch deren Identifikatoren.</t>
+  </si>
+  <si>
+    <t>Ein Name kann eine Komponente beschreiben, jedoch ist in STRENDCAT kein allgemeines Namensattribut vorhanden.</t>
+  </si>
+  <si>
+    <t>Beide referenzieren das Reaktionsgefäß, in dem ein Objekt verwendet wird.</t>
+  </si>
+  <si>
+    <t>Beide ermöglichen die Zuordnung zu Personen, Forschungsgruppen oder anderen verantwortlichen Akteuren, wenngleich mit unterschiedlicher Rolle.</t>
+  </si>
+  <si>
+    <t>Der Familienname ist ein personenbezogenes Attribut; supplied_by kann einen Akteur bzw. eine Forschungsgruppe benennen.</t>
+  </si>
+  <si>
+    <t>Der Vorname kann Teil der Benennung eines verantwortlichen Akteurs sein, wird aber nicht direkt durch STRENDCAT modelliert.</t>
+  </si>
+  <si>
+    <t>Kontaktinformationen eines Autors sind nur sehr indirekt mit der Angabe eines Lieferanten oder Forschungsakteurs vergleichbar.</t>
+  </si>
+  <si>
+    <t>Beide erfassen einen Zeitpunkt bzw. ein Datum, allerdings für die Dokumenterstellung beziehungsweise den Beginn einer Lagerung.</t>
+  </si>
+  <si>
+    <t>Autoren eines Dokuments und bereitstellende Akteure sind beides Attributionen zu Personen oder Organisationen.</t>
+  </si>
+  <si>
+    <t>Beide sind Datumsangaben, aber die fachliche Bedeutung unterscheidet sich deutlich.</t>
+  </si>
+  <si>
+    <t>Beide sind beschreibende Textfelder, aber STRENDCAT enthält kein allgemeines Titel- oder Namensfeld für Dokumente.</t>
+  </si>
+  <si>
+    <t>Referenzen und Quellenangaben können Akteure oder externe Ressourcen dokumentieren, allerdings gibt es kein direktes Zitationsfeld in der Datengrundlage.</t>
+  </si>
+  <si>
+    <t>Die Referenz auf eine Spezies in einer Gleichung entspricht am ehesten einer chemischen Komponente der biokatalytischen Reaktion.</t>
+  </si>
+  <si>
+    <t>Die ID identifiziert eine Messung; STRENDCAT modelliert dafür den Messprozess, jedoch kein eigenes Identifikatorattribut.</t>
+  </si>
+  <si>
+    <t>Modifier und Reaktanten sind Spezies bzw. Komponenten, die im Reaktionskontext verwendet werden.</t>
+  </si>
+  <si>
+    <t>Ein Parameter kann ein kinetischer Parameter sein, aber die reine Identifikation eines Parameters wird nicht direkt abgebildet.</t>
+  </si>
+  <si>
+    <t>Proteine, insbesondere Enzyme, entsprechen sehr gut dem STRENDCAT-Konzept eines Biokatalysators.</t>
+  </si>
+  <si>
+    <t>Beide beschreiben Kennungen für biochemisch relevante Entitäten, obwohl eine Protein-ID wie UniProt nicht mit einer EC-Nummer gleichzusetzen ist.</t>
+  </si>
+  <si>
+    <t>Der Name bezeichnet ein Protein beziehungsweise Enzym und kann daher dem Biokatalysator zugeordnet werden.</t>
+  </si>
+  <si>
+    <t>Beide beschreiben einen Organismusbezug eines biokatalytisch relevanten Proteins, auch wenn EnzymeML konkret den Expressionswirt meint.</t>
+  </si>
+  <si>
+    <t>Beide können externe Herkunftsinformationen dokumentieren, jedoch fehlt in STRENDCAT ein direktes Literaturreferenzfeld.</t>
+  </si>
+  <si>
+    <t>Beide beschreiben unmittelbar die Aminosäuresequenz eines Proteins.</t>
+  </si>
+  <si>
+    <t>Beide stellen die Verbindung eines Proteins beziehungsweise Biokatalysators zum verwendeten Reaktionsgefäß her.</t>
+  </si>
+  <si>
+    <t>Die ID identifiziert eine Reaktion; die STRENDCAT-Klasse repräsentiert die biokatalytische Reaktion selbst.</t>
+  </si>
+  <si>
+    <t>Ein ReactionElement referenziert eine beteiligte Spezies und passt daher zu einer Reaktionskomponente.</t>
+  </si>
+  <si>
+    <t>Beide sind Identifikatoren chemisch relevanter Entitäten, aber eine Small-Molecule-ID ist fachlich nicht direkt eine EC-Nummer.</t>
+  </si>
+  <si>
+    <t>Der Name einer kleinen Molekülart bezeichnet typischerweise eine chemische Komponente der Reaktionsmischung.</t>
+  </si>
+  <si>
+    <t>Referenzen zu einem Molekül und Informationen über dessen Bereitsteller sind nur schwach verwandt.</t>
+  </si>
+  <si>
+    <t>Beide verknüpfen ein kleines Molekül mit dem Reaktionsgefäß, in dem es eingesetzt wurde.</t>
+  </si>
+  <si>
+    <t>Eine Variable kann unter anderem einen Zeitwert repräsentieren; die reine ID einer Variable besitzt jedoch keine direkte Entsprechung.</t>
+  </si>
+  <si>
+    <t>Beide repräsentieren Behälter zur Durchführung biologischer oder chemischer Experimente beziehungsweise Reaktionen.</t>
+  </si>
+  <si>
+    <t>Beide beziehen sich auf die Identifikation oder Referenzierung eines verwendeten Reaktionsgefäßes.</t>
+  </si>
+  <si>
+    <t>Der Name beschreibt ein Reaktionsgefäß, auch wenn STRENDCAT kein separates Namensattribut dafür vorsieht.</t>
+  </si>
+  <si>
+    <t>Beide erfassen ein Volumen; STRENDCAT beschreibt allerdings das Volumen einer Probe und nicht ausdrücklich das Gesamtvolumen des Gefäßes.</t>
+  </si>
+  <si>
+    <t>Campus_AI-based: STRENDCAT_entity_name</t>
+  </si>
+  <si>
+    <t>Campus_AI-based: Score</t>
+  </si>
+  <si>
+    <t>Campus_AI-based: Kurzbegruendung</t>
   </si>
 </sst>
 </file>
@@ -2301,7 +2418,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2309,6 +2426,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2354,7 +2472,15 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2684,7 +2810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21EF845A-581D-4E43-B9D4-125E9A870B43}">
-  <dimension ref="A1:M197"/>
+  <dimension ref="A1:P197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -2698,10 +2824,12 @@
     <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="1.5703125" customWidth="1"/>
     <col min="11" max="11" width="34.7109375" customWidth="1"/>
-    <col min="12" max="12" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2737,10 +2865,17 @@
         <v>590</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="P1" s="2"/>
+    </row>
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2760,23 +2895,26 @@
         <v>493</v>
       </c>
       <c r="H2" t="s">
-        <v>494</v>
-      </c>
-      <c r="I2" t="s">
-        <v>495</v>
-      </c>
-      <c r="J2" t="s">
-        <v>496</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>497</v>
+        <v>591</v>
+      </c>
+      <c r="K2" t="s">
+        <v>592</v>
       </c>
       <c r="L2" t="e">
         <f>_xlfn.XMATCH(I2,$C$2:$C$197)</f>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>227</v>
+      </c>
+      <c r="N2" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="O2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2796,23 +2934,32 @@
         <v>493</v>
       </c>
       <c r="H3" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="I3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J3" t="s">
         <v>496</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L3" t="e">
-        <f t="shared" ref="L3:L35" si="0">_xlfn.XMATCH(I3,$C$2:$C$197)</f>
+        <f>_xlfn.XMATCH(I3,$C$2:$C$197)</f>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M3" t="s">
+        <v>236</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="O3" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2832,23 +2979,32 @@
         <v>493</v>
       </c>
       <c r="H4" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="I4" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J4" t="s">
         <v>496</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="L4" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L4:L36" si="0">_xlfn.XMATCH(I4,$C$2:$C$197)</f>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M4" t="s">
+        <v>227</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="O4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2868,23 +3024,32 @@
         <v>493</v>
       </c>
       <c r="H5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="I5" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="J5" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="L5" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M5" t="s">
+        <v>476</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O5" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2904,23 +3069,32 @@
         <v>493</v>
       </c>
       <c r="H6" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="I6" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="J6" t="s">
         <v>505</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="L6" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" t="s">
+        <v>465</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0.36</v>
+      </c>
+      <c r="O6" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2940,23 +3114,32 @@
         <v>493</v>
       </c>
       <c r="H7" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="I7" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J7" t="s">
         <v>505</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="L7" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M7" t="s">
+        <v>465</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O7" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2976,23 +3159,32 @@
         <v>493</v>
       </c>
       <c r="H8" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="I8" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J8" t="s">
         <v>505</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="L8" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M8" t="s">
+        <v>465</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="O8" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -3012,23 +3204,32 @@
         <v>493</v>
       </c>
       <c r="H9" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="I9" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J9" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="L9" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M9" t="s">
+        <v>465</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -3048,23 +3249,32 @@
         <v>493</v>
       </c>
       <c r="H10" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="I10" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="J10" t="s">
         <v>518</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="L10" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M10" t="s">
+        <v>462</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="O10" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -3084,23 +3294,32 @@
         <v>493</v>
       </c>
       <c r="H11" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="I11" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="J11" t="s">
         <v>518</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="L11" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M11" t="s">
+        <v>465</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="O11" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -3120,23 +3339,32 @@
         <v>493</v>
       </c>
       <c r="H12" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="I12" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="J12" t="s">
         <v>518</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="L12" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M12" t="s">
+        <v>462</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="O12" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -3156,23 +3384,32 @@
         <v>493</v>
       </c>
       <c r="H13" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="I13" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J13" t="s">
         <v>518</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="L13" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M13" t="s">
+        <v>418</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="O13" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -3192,23 +3429,32 @@
         <v>493</v>
       </c>
       <c r="H14" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="I14" t="s">
-        <v>495</v>
+        <v>530</v>
       </c>
       <c r="J14" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="L14" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M14" t="s">
+        <v>465</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0.12</v>
+      </c>
+      <c r="O14" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -3228,23 +3474,32 @@
         <v>493</v>
       </c>
       <c r="H15" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="I15" t="s">
         <v>495</v>
       </c>
       <c r="J15" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="L15" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M15" t="s">
+        <v>227</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="O15" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -3264,23 +3519,32 @@
         <v>493</v>
       </c>
       <c r="H16" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="I16" t="s">
         <v>495</v>
       </c>
       <c r="J16" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="L16" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M16" t="s">
+        <v>86</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="O16" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -3300,23 +3564,32 @@
         <v>493</v>
       </c>
       <c r="H17" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="I17" t="s">
         <v>495</v>
       </c>
       <c r="J17" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="L17" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M17" t="s">
+        <v>227</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O17" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -3336,23 +3609,32 @@
         <v>493</v>
       </c>
       <c r="H18" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="I18" t="s">
-        <v>545</v>
+        <v>495</v>
       </c>
       <c r="J18" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="L18" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M18" t="s">
+        <v>70</v>
+      </c>
+      <c r="N18" s="5">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O18" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3372,23 +3654,32 @@
         <v>493</v>
       </c>
       <c r="H19" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="I19" t="s">
-        <v>495</v>
+        <v>545</v>
       </c>
       <c r="J19" t="s">
         <v>546</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="L19" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M19" t="s">
+        <v>6</v>
+      </c>
+      <c r="N19" s="5">
+        <v>0.8</v>
+      </c>
+      <c r="O19" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -3408,23 +3699,32 @@
         <v>493</v>
       </c>
       <c r="H20" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="I20" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J20" t="s">
         <v>546</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="L20" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" t="s">
+        <v>209</v>
+      </c>
+      <c r="N20" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="O20" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -3444,23 +3744,32 @@
         <v>493</v>
       </c>
       <c r="H21" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="I21" t="s">
-        <v>553</v>
+        <v>499</v>
       </c>
       <c r="J21" t="s">
         <v>546</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="L21" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M21" t="s">
+        <v>6</v>
+      </c>
+      <c r="N21" s="5">
+        <v>0.34</v>
+      </c>
+      <c r="O21" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -3480,23 +3789,32 @@
         <v>493</v>
       </c>
       <c r="H22" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="I22" t="s">
-        <v>530</v>
+        <v>553</v>
       </c>
       <c r="J22" t="s">
         <v>546</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="L22" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M22" t="s">
+        <v>395</v>
+      </c>
+      <c r="N22" s="5">
+        <v>0.77</v>
+      </c>
+      <c r="O22" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -3516,23 +3834,32 @@
         <v>493</v>
       </c>
       <c r="H23" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="I23" t="s">
-        <v>558</v>
+        <v>530</v>
       </c>
       <c r="J23" t="s">
         <v>546</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="L23" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M23" t="s">
+        <v>465</v>
+      </c>
+      <c r="N23" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="O23" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -3552,23 +3879,32 @@
         <v>493</v>
       </c>
       <c r="H24" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="I24" t="s">
-        <v>495</v>
+        <v>558</v>
       </c>
       <c r="J24" t="s">
         <v>546</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="L24" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M24" t="s">
+        <v>433</v>
+      </c>
+      <c r="N24" s="5">
+        <v>0.98</v>
+      </c>
+      <c r="O24" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -3588,23 +3924,32 @@
         <v>493</v>
       </c>
       <c r="H25" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="I25" t="s">
         <v>495</v>
       </c>
       <c r="J25" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="L25" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M25" t="s">
+        <v>476</v>
+      </c>
+      <c r="N25" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="O25" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -3624,23 +3969,32 @@
         <v>493</v>
       </c>
       <c r="H26" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="I26" t="s">
         <v>495</v>
       </c>
       <c r="J26" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>540</v>
+        <v>564</v>
       </c>
       <c r="L26" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+      <c r="N26" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="O26" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -3660,23 +4014,32 @@
         <v>493</v>
       </c>
       <c r="H27" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="I27" t="s">
         <v>495</v>
       </c>
       <c r="J27" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>569</v>
+        <v>540</v>
       </c>
       <c r="L27" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M27" t="s">
+        <v>227</v>
+      </c>
+      <c r="N27" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="O27" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -3696,23 +4059,32 @@
         <v>493</v>
       </c>
       <c r="H28" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="I28" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J28" t="s">
         <v>568</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="L28" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M28" t="s">
+        <v>209</v>
+      </c>
+      <c r="N28" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="O28" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -3732,23 +4104,32 @@
         <v>493</v>
       </c>
       <c r="H29" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="I29" t="s">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="J29" t="s">
         <v>568</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="L29" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M29" t="s">
+        <v>227</v>
+      </c>
+      <c r="N29" s="5">
+        <v>0.31</v>
+      </c>
+      <c r="O29" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -3768,23 +4149,32 @@
         <v>493</v>
       </c>
       <c r="H30" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="I30" t="s">
-        <v>495</v>
+        <v>530</v>
       </c>
       <c r="J30" t="s">
         <v>568</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="L30" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M30" t="s">
+        <v>465</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -3804,23 +4194,32 @@
         <v>493</v>
       </c>
       <c r="H31" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="I31" t="s">
         <v>495</v>
       </c>
       <c r="J31" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="L31" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M31" t="s">
+        <v>476</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="O31" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -3840,23 +4239,32 @@
         <v>493</v>
       </c>
       <c r="H32" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="I32" t="s">
-        <v>580</v>
+        <v>495</v>
       </c>
       <c r="J32" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="L32" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M32" t="s">
+        <v>364</v>
+      </c>
+      <c r="N32" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="O32" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -3876,23 +4284,32 @@
         <v>493</v>
       </c>
       <c r="H33" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="I33" t="s">
-        <v>495</v>
+        <v>580</v>
       </c>
       <c r="J33" t="s">
         <v>581</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="L33" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M33" t="s">
+        <v>117</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0.95</v>
+      </c>
+      <c r="O33" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -3912,23 +4329,32 @@
         <v>493</v>
       </c>
       <c r="H34" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I34" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J34" t="s">
         <v>581</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="L34" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M34" t="s">
+        <v>476</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="O34" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -3948,23 +4374,32 @@
         <v>493</v>
       </c>
       <c r="H35" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="I35" t="s">
-        <v>588</v>
+        <v>499</v>
       </c>
       <c r="J35" t="s">
         <v>581</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="L35" t="e">
         <f t="shared" si="0"/>
         <v>#N/A</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M35" t="s">
+        <v>117</v>
+      </c>
+      <c r="N35" s="5">
+        <v>0.42</v>
+      </c>
+      <c r="O35" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -3980,8 +4415,36 @@
       <c r="E36" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G36" t="s">
+        <v>493</v>
+      </c>
+      <c r="H36" t="s">
+        <v>587</v>
+      </c>
+      <c r="I36" t="s">
+        <v>588</v>
+      </c>
+      <c r="J36" t="s">
+        <v>581</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="L36" t="e">
+        <f t="shared" si="0"/>
+        <v>#N/A</v>
+      </c>
+      <c r="M36" t="s">
+        <v>325</v>
+      </c>
+      <c r="N36" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="O36" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -3998,7 +4461,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -4015,7 +4478,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -4032,7 +4495,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -4049,7 +4512,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -4066,7 +4529,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -4083,7 +4546,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -4100,7 +4563,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -4117,7 +4580,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -4131,7 +4594,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -4145,7 +4608,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -4159,7 +4622,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -6260,6 +6723,14 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="N2:N36">
+    <cfRule type="cellIs" priority="2" operator="greaterThan">
+      <formula>"0.75"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+      <formula>0.75</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/strendcat_biocatalysis/schema/comparison.xlsx
+++ b/src/strendcat_biocatalysis/schema/comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\StrenDCAT-Biocatalysis\src\strendcat_biocatalysis\schema\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B0EAA9-FBDE-4C11-A5F2-6214135138A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEE346C-1E55-45DB-BF11-F55E335FDDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0DE9B59C-CD8C-42BC-9FD3-3BA2E451A179}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1084" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="633">
   <si>
     <t>file</t>
   </si>
@@ -1922,13 +1922,19 @@
     <t>Beide erfassen ein Volumen; STRENDCAT beschreibt allerdings das Volumen einer Probe und nicht ausdrücklich das Gesamtvolumen des Gefäßes.</t>
   </si>
   <si>
-    <t>Campus_AI-based: STRENDCAT_entity_name</t>
-  </si>
-  <si>
     <t>Campus_AI-based: Score</t>
   </si>
   <si>
     <t>Campus_AI-based: Kurzbegruendung</t>
+  </si>
+  <si>
+    <t>Campus_AI-based: best matching STRENDCAT_entity_name</t>
+  </si>
+  <si>
+    <t>best matching STRENDCAT_entity_description</t>
+  </si>
+  <si>
+    <t>best matching STRENDCAT_entity_uri</t>
   </si>
 </sst>
 </file>
@@ -2472,7 +2478,21 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2810,7 +2830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21EF845A-581D-4E43-B9D4-125E9A870B43}">
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:R197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
@@ -2818,18 +2838,20 @@
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="2" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="4"/>
+    <col min="6" max="6" width="3.140625" style="4" customWidth="1"/>
     <col min="7" max="7" width="8.5703125" customWidth="1"/>
     <col min="8" max="8" width="31.42578125" customWidth="1"/>
     <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="1.5703125" customWidth="1"/>
     <col min="11" max="11" width="34.7109375" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.85546875" customWidth="1"/>
     <col min="13" max="13" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="42.28515625" customWidth="1"/>
+    <col min="15" max="15" width="31.140625" customWidth="1"/>
+    <col min="16" max="16" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2865,17 +2887,23 @@
         <v>590</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="P1" s="2"/>
-    </row>
-    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R1" s="2"/>
+    </row>
+    <row r="2" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2907,14 +2935,22 @@
       <c r="M2" t="s">
         <v>227</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" t="str">
+        <f>VLOOKUP(M2,$B$2:$E$196,2)</f>
+        <v>prov:used</v>
+      </c>
+      <c r="O2" t="str">
+        <f>VLOOKUP(M2,$B$2:$E$196,4)</f>
+        <v>The chemical components present in the reaction mixture.</v>
+      </c>
+      <c r="P2" s="5">
         <v>0.74</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Q2" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2952,14 +2988,22 @@
       <c r="M3" t="s">
         <v>236</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" t="str">
+        <f t="shared" ref="N3:N36" si="0">VLOOKUP(M3,$B$2:$E$196,2)</f>
+        <v>RO:0000087</v>
+      </c>
+      <c r="O3" t="str">
+        <f t="shared" ref="N3:O36" si="1">VLOOKUP(M3,$B$2:$E$196,4)</f>
+        <v>The functional role of this component in the biocatalytic reaction. Optional per P-002 — a structural converter may leave this unpopulated</v>
+      </c>
+      <c r="P3" s="5">
         <v>0.18</v>
       </c>
-      <c r="O3" t="s">
+      <c r="Q3" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2991,20 +3035,28 @@
         <v>500</v>
       </c>
       <c r="L4" t="e">
-        <f t="shared" ref="L4:L36" si="0">_xlfn.XMATCH(I4,$C$2:$C$197)</f>
+        <f t="shared" ref="L4:L36" si="2">_xlfn.XMATCH(I4,$C$2:$C$197)</f>
         <v>#N/A</v>
       </c>
       <c r="M4" t="s">
         <v>227</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:used</v>
+      </c>
+      <c r="O4" t="str">
+        <f t="shared" si="1"/>
+        <v>The chemical components present in the reaction mixture.</v>
+      </c>
+      <c r="P4" s="5">
         <v>0.15</v>
       </c>
-      <c r="O4" t="s">
+      <c r="Q4" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -3036,20 +3088,28 @@
         <v>502</v>
       </c>
       <c r="L5" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M5" t="s">
         <v>476</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAssociatedWith</v>
+      </c>
+      <c r="O5" t="str">
+        <f t="shared" si="1"/>
+        <v>The reaction vessel in which the biocatalytic reaction took place.</v>
+      </c>
+      <c r="P5" s="5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -3081,20 +3141,28 @@
         <v>506</v>
       </c>
       <c r="L6" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M6" t="s">
         <v>465</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAttributedTo</v>
+      </c>
+      <c r="O6" t="str">
+        <f t="shared" si="1"/>
+        <v>The commercial supplier or research group that provided this material. Maps to the STRENDA supplier string via Agent.name (foaf:name).</v>
+      </c>
+      <c r="P6" s="5">
         <v>0.36</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -3126,20 +3194,28 @@
         <v>509</v>
       </c>
       <c r="L7" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M7" t="s">
         <v>465</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAttributedTo</v>
+      </c>
+      <c r="O7" t="str">
+        <f t="shared" si="1"/>
+        <v>The commercial supplier or research group that provided this material. Maps to the STRENDA supplier string via Agent.name (foaf:name).</v>
+      </c>
+      <c r="P7" s="5">
         <v>0.13</v>
       </c>
-      <c r="O7" t="s">
+      <c r="Q7" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -3171,20 +3247,28 @@
         <v>512</v>
       </c>
       <c r="L8" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M8" t="s">
         <v>465</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAttributedTo</v>
+      </c>
+      <c r="O8" t="str">
+        <f t="shared" si="1"/>
+        <v>The commercial supplier or research group that provided this material. Maps to the STRENDA supplier string via Agent.name (foaf:name).</v>
+      </c>
+      <c r="P8" s="5">
         <v>0.13</v>
       </c>
-      <c r="O8" t="s">
+      <c r="Q8" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -3216,20 +3300,28 @@
         <v>515</v>
       </c>
       <c r="L9" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M9" t="s">
         <v>465</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAttributedTo</v>
+      </c>
+      <c r="O9" t="str">
+        <f t="shared" si="1"/>
+        <v>The commercial supplier or research group that provided this material. Maps to the STRENDA supplier string via Agent.name (foaf:name).</v>
+      </c>
+      <c r="P9" s="5">
         <v>0.1</v>
       </c>
-      <c r="O9" t="s">
+      <c r="Q9" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -3261,20 +3353,28 @@
         <v>519</v>
       </c>
       <c r="L10" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M10" t="s">
         <v>462</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" t="str">
+        <f t="shared" si="0"/>
+        <v>dcterms:created</v>
+      </c>
+      <c r="O10" t="str">
+        <f t="shared" si="1"/>
+        <v>The date since which the material entity has been stored.</v>
+      </c>
+      <c r="P10" s="5">
         <v>0.23</v>
       </c>
-      <c r="O10" t="s">
+      <c r="Q10" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -3306,20 +3406,28 @@
         <v>522</v>
       </c>
       <c r="L11" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M11" t="s">
         <v>465</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAttributedTo</v>
+      </c>
+      <c r="O11" t="str">
+        <f t="shared" si="1"/>
+        <v>The commercial supplier or research group that provided this material. Maps to the STRENDA supplier string via Agent.name (foaf:name).</v>
+      </c>
+      <c r="P11" s="5">
         <v>0.34</v>
       </c>
-      <c r="O11" t="s">
+      <c r="Q11" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -3351,20 +3459,28 @@
         <v>525</v>
       </c>
       <c r="L12" t="e">
-        <f t="shared" si="0"/>
+        <f>_xlfn.XMATCH(I12,$C$2:$C$197)</f>
         <v>#N/A</v>
       </c>
       <c r="M12" t="s">
         <v>462</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" t="str">
+        <f t="shared" si="0"/>
+        <v>dcterms:created</v>
+      </c>
+      <c r="O12" t="str">
+        <f t="shared" si="1"/>
+        <v>The date since which the material entity has been stored.</v>
+      </c>
+      <c r="P12" s="5">
         <v>0.12</v>
       </c>
-      <c r="O12" t="s">
+      <c r="Q12" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -3396,20 +3512,28 @@
         <v>528</v>
       </c>
       <c r="L13" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M13" t="s">
         <v>418</v>
       </c>
-      <c r="N13" s="5">
+      <c r="N13" t="str">
+        <f t="shared" si="0"/>
+        <v>SIO:000008</v>
+      </c>
+      <c r="O13" t="str">
+        <f t="shared" si="1"/>
+        <v>Description of the tubular flow reactor type (e.g. packed bed reactor, plug flow reactor, microreactor).</v>
+      </c>
+      <c r="P13" s="5">
         <v>0.09</v>
       </c>
-      <c r="O13" t="s">
+      <c r="Q13" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -3441,20 +3565,28 @@
         <v>531</v>
       </c>
       <c r="L14" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M14" t="s">
         <v>465</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAttributedTo</v>
+      </c>
+      <c r="O14" t="str">
+        <f t="shared" si="1"/>
+        <v>The commercial supplier or research group that provided this material. Maps to the STRENDA supplier string via Agent.name (foaf:name).</v>
+      </c>
+      <c r="P14" s="5">
         <v>0.12</v>
       </c>
-      <c r="O14" t="s">
+      <c r="Q14" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -3486,20 +3618,28 @@
         <v>534</v>
       </c>
       <c r="L15" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M15" t="s">
         <v>227</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:used</v>
+      </c>
+      <c r="O15" t="str">
+        <f t="shared" si="1"/>
+        <v>The chemical components present in the reaction mixture.</v>
+      </c>
+      <c r="P15" s="5">
         <v>0.61</v>
       </c>
-      <c r="O15" t="s">
+      <c r="Q15" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -3531,20 +3671,28 @@
         <v>537</v>
       </c>
       <c r="L16" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M16" t="s">
         <v>86</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N16" t="str">
+        <f t="shared" si="0"/>
+        <v>OBI:0000070</v>
+      </c>
+      <c r="O16" t="str">
+        <f t="shared" si="1"/>
+        <v>A planned process that has the objective to produce information about a material entity by examining it. (OBI:0000070 stub)</v>
+      </c>
+      <c r="P16" s="5">
         <v>0.31</v>
       </c>
-      <c r="O16" t="s">
+      <c r="Q16" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -3576,20 +3724,28 @@
         <v>540</v>
       </c>
       <c r="L17" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M17" t="s">
         <v>227</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:used</v>
+      </c>
+      <c r="O17" t="str">
+        <f t="shared" si="1"/>
+        <v>The chemical components present in the reaction mixture.</v>
+      </c>
+      <c r="P17" s="5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="O17" t="s">
+      <c r="Q17" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -3621,20 +3777,28 @@
         <v>543</v>
       </c>
       <c r="L18" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M18" t="s">
         <v>70</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" t="str">
+        <f t="shared" si="0"/>
+        <v>SIO:000144</v>
+      </c>
+      <c r="O18" t="str">
+        <f t="shared" si="1"/>
+        <v>A wrapper class grouping kinetic parameters determined for a biocatalytic reaction. Km and kcat values must be determined by varying all substrate concentrations to obtain true (non-apparent) values.</v>
+      </c>
+      <c r="P18" s="5">
         <v>0.28999999999999998</v>
       </c>
-      <c r="O18" t="s">
+      <c r="Q18" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -3666,20 +3830,28 @@
         <v>547</v>
       </c>
       <c r="L19" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M19" t="s">
         <v>6</v>
       </c>
-      <c r="N19" s="5">
+      <c r="N19" t="str">
+        <f t="shared" si="0"/>
+        <v>CHEBI:35233</v>
+      </c>
+      <c r="O19" t="str">
+        <f t="shared" si="1"/>
+        <v>An enzyme or cell that catalyzes a biocatalytic reaction. Subclass of Catalyst (AgenticEntity). The physical form in which it is applied is described by an associated BiocatalystPreparation.</v>
+      </c>
+      <c r="P19" s="5">
         <v>0.8</v>
       </c>
-      <c r="O19" t="s">
+      <c r="Q19" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -3711,20 +3883,28 @@
         <v>549</v>
       </c>
       <c r="L20" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M20" t="s">
         <v>209</v>
       </c>
-      <c r="N20" s="5">
+      <c r="N20" t="str">
+        <f t="shared" si="0"/>
+        <v>CHEMINF:000447</v>
+      </c>
+      <c r="O20" t="str">
+        <f t="shared" si="1"/>
+        <v>A seven-digit identifier for chemical substances for regulatory purposes within the European Union.</v>
+      </c>
+      <c r="P20" s="5">
         <v>0.3</v>
       </c>
-      <c r="O20" t="s">
+      <c r="Q20" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -3756,20 +3936,28 @@
         <v>551</v>
       </c>
       <c r="L21" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M21" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="5">
+      <c r="N21" t="str">
+        <f t="shared" si="0"/>
+        <v>CHEBI:35233</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="1"/>
+        <v>An enzyme or cell that catalyzes a biocatalytic reaction. Subclass of Catalyst (AgenticEntity). The physical form in which it is applied is described by an associated BiocatalystPreparation.</v>
+      </c>
+      <c r="P21" s="5">
         <v>0.34</v>
       </c>
-      <c r="O21" t="s">
+      <c r="Q21" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -3801,20 +3989,28 @@
         <v>554</v>
       </c>
       <c r="L22" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M22" t="s">
         <v>395</v>
       </c>
-      <c r="N22" s="5">
+      <c r="N22" t="str">
+        <f t="shared" si="0"/>
+        <v>SIO:010079</v>
+      </c>
+      <c r="O22" t="str">
+        <f t="shared" si="1"/>
+        <v>The genus and species of the organism from which the biocatalyst is derived or isolated.</v>
+      </c>
+      <c r="P22" s="5">
         <v>0.77</v>
       </c>
-      <c r="O22" t="s">
+      <c r="Q22" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -3846,20 +4042,28 @@
         <v>556</v>
       </c>
       <c r="L23" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M23" t="s">
         <v>465</v>
       </c>
-      <c r="N23" s="5">
+      <c r="N23" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAttributedTo</v>
+      </c>
+      <c r="O23" t="str">
+        <f t="shared" si="1"/>
+        <v>The commercial supplier or research group that provided this material. Maps to the STRENDA supplier string via Agent.name (foaf:name).</v>
+      </c>
+      <c r="P23" s="5">
         <v>0.1</v>
       </c>
-      <c r="O23" t="s">
+      <c r="Q23" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -3891,20 +4095,28 @@
         <v>559</v>
       </c>
       <c r="L24" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M24" t="s">
         <v>433</v>
       </c>
-      <c r="N24" s="5">
+      <c r="N24" t="str">
+        <f t="shared" si="0"/>
+        <v>SIO:000008</v>
+      </c>
+      <c r="O24" t="str">
+        <f t="shared" si="1"/>
+        <v>The method used to separate the secreted enzyme supernatant from cells (e.g. centrifugation, filtration).</v>
+      </c>
+      <c r="P24" s="5">
         <v>0.98</v>
       </c>
-      <c r="O24" t="s">
+      <c r="Q24" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -3936,20 +4148,28 @@
         <v>561</v>
       </c>
       <c r="L25" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M25" t="s">
         <v>476</v>
       </c>
-      <c r="N25" s="5">
+      <c r="N25" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAssociatedWith</v>
+      </c>
+      <c r="O25" t="str">
+        <f t="shared" si="1"/>
+        <v>The reaction vessel in which the biocatalytic reaction took place.</v>
+      </c>
+      <c r="P25" s="5">
         <v>0.6</v>
       </c>
-      <c r="O25" t="s">
+      <c r="Q25" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -3981,20 +4201,28 @@
         <v>564</v>
       </c>
       <c r="L26" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M26" t="s">
         <v>14</v>
       </c>
-      <c r="N26" s="5">
+      <c r="N26" t="str">
+        <f t="shared" si="0"/>
+        <v>SIO:010345</v>
+      </c>
+      <c r="O26" t="str">
+        <f t="shared" si="1"/>
+        <v>A ChemicalReaction that is catalyzed by a Biocatalyst (enzyme or whole cell). Evaluated by a BiocatalyticExperiment. Carries reaction conditions, phase system, and result attributes.</v>
+      </c>
+      <c r="P26" s="5">
         <v>0.37</v>
       </c>
-      <c r="O26" t="s">
+      <c r="Q26" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -4026,20 +4254,28 @@
         <v>540</v>
       </c>
       <c r="L27" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M27" t="s">
         <v>227</v>
       </c>
-      <c r="N27" s="5">
+      <c r="N27" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:used</v>
+      </c>
+      <c r="O27" t="str">
+        <f t="shared" si="1"/>
+        <v>The chemical components present in the reaction mixture.</v>
+      </c>
+      <c r="P27" s="5">
         <v>0.65</v>
       </c>
-      <c r="O27" t="s">
+      <c r="Q27" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -4071,20 +4307,28 @@
         <v>569</v>
       </c>
       <c r="L28" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M28" t="s">
         <v>209</v>
       </c>
-      <c r="N28" s="5">
+      <c r="N28" t="str">
+        <f t="shared" si="0"/>
+        <v>CHEMINF:000447</v>
+      </c>
+      <c r="O28" t="str">
+        <f t="shared" si="1"/>
+        <v>A seven-digit identifier for chemical substances for regulatory purposes within the European Union.</v>
+      </c>
+      <c r="P28" s="5">
         <v>0.25</v>
       </c>
-      <c r="O28" t="s">
+      <c r="Q28" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -4116,20 +4360,28 @@
         <v>571</v>
       </c>
       <c r="L29" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M29" t="s">
         <v>227</v>
       </c>
-      <c r="N29" s="5">
+      <c r="N29" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:used</v>
+      </c>
+      <c r="O29" t="str">
+        <f t="shared" si="1"/>
+        <v>The chemical components present in the reaction mixture.</v>
+      </c>
+      <c r="P29" s="5">
         <v>0.31</v>
       </c>
-      <c r="O29" t="s">
+      <c r="Q29" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -4161,20 +4413,28 @@
         <v>573</v>
       </c>
       <c r="L30" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M30" t="s">
         <v>465</v>
       </c>
-      <c r="N30" s="5">
+      <c r="N30" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAttributedTo</v>
+      </c>
+      <c r="O30" t="str">
+        <f t="shared" si="1"/>
+        <v>The commercial supplier or research group that provided this material. Maps to the STRENDA supplier string via Agent.name (foaf:name).</v>
+      </c>
+      <c r="P30" s="5">
         <v>0.1</v>
       </c>
-      <c r="O30" t="s">
+      <c r="Q30" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -4206,20 +4466,28 @@
         <v>575</v>
       </c>
       <c r="L31" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M31" t="s">
         <v>476</v>
       </c>
-      <c r="N31" s="5">
+      <c r="N31" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAssociatedWith</v>
+      </c>
+      <c r="O31" t="str">
+        <f t="shared" si="1"/>
+        <v>The reaction vessel in which the biocatalytic reaction took place.</v>
+      </c>
+      <c r="P31" s="5">
         <v>0.6</v>
       </c>
-      <c r="O31" t="s">
+      <c r="Q31" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -4251,20 +4519,28 @@
         <v>578</v>
       </c>
       <c r="L32" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M32" t="s">
         <v>364</v>
       </c>
-      <c r="N32" s="5">
+      <c r="N32" t="str">
+        <f t="shared" si="0"/>
+        <v>SIO:000008</v>
+      </c>
+      <c r="O32" t="str">
+        <f t="shared" si="1"/>
+        <v>A time value as a numeric quantity.</v>
+      </c>
+      <c r="P32" s="5">
         <v>0.11</v>
       </c>
-      <c r="O32" t="s">
+      <c r="Q32" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -4296,20 +4572,28 @@
         <v>582</v>
       </c>
       <c r="L33" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M33" t="s">
         <v>117</v>
       </c>
-      <c r="N33" s="5">
+      <c r="N33" t="str">
+        <f t="shared" si="0"/>
+        <v>AFE:0000153</v>
+      </c>
+      <c r="O33" t="str">
+        <f t="shared" si="1"/>
+        <v>A reactor is a container for controlling a biological or chemical reaction or process. [Allotrope]</v>
+      </c>
+      <c r="P33" s="5">
         <v>0.95</v>
       </c>
-      <c r="O33" t="s">
+      <c r="Q33" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -4341,20 +4625,28 @@
         <v>584</v>
       </c>
       <c r="L34" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M34" t="s">
         <v>476</v>
       </c>
-      <c r="N34" s="5">
+      <c r="N34" t="str">
+        <f t="shared" si="0"/>
+        <v>prov:wasAssociatedWith</v>
+      </c>
+      <c r="O34" t="str">
+        <f t="shared" si="1"/>
+        <v>The reaction vessel in which the biocatalytic reaction took place.</v>
+      </c>
+      <c r="P34" s="5">
         <v>0.46</v>
       </c>
-      <c r="O34" t="s">
+      <c r="Q34" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -4386,20 +4678,28 @@
         <v>586</v>
       </c>
       <c r="L35" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M35" t="s">
         <v>117</v>
       </c>
-      <c r="N35" s="5">
+      <c r="N35" t="str">
+        <f t="shared" si="0"/>
+        <v>AFE:0000153</v>
+      </c>
+      <c r="O35" t="str">
+        <f t="shared" si="1"/>
+        <v>A reactor is a container for controlling a biological or chemical reaction or process. [Allotrope]</v>
+      </c>
+      <c r="P35" s="5">
         <v>0.42</v>
       </c>
-      <c r="O35" t="s">
+      <c r="Q35" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -4431,20 +4731,28 @@
         <v>589</v>
       </c>
       <c r="L36" t="e">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>#N/A</v>
       </c>
       <c r="M36" t="s">
         <v>325</v>
       </c>
-      <c r="N36" s="5">
+      <c r="N36" t="str">
+        <f t="shared" si="0"/>
+        <v>SIO:000008</v>
+      </c>
+      <c r="O36" t="str">
+        <f t="shared" si="1"/>
+        <v>Volume of the collected sample.</v>
+      </c>
+      <c r="P36" s="5">
         <v>0.5</v>
       </c>
-      <c r="O36" t="s">
+      <c r="Q36" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -4461,7 +4769,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -4478,7 +4786,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -4495,7 +4803,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -4512,7 +4820,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -4529,7 +4837,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -4546,7 +4854,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -4563,7 +4871,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -4580,7 +4888,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -4594,7 +4902,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -4608,7 +4916,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -4622,7 +4930,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -6723,11 +7031,11 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N2:N36">
-    <cfRule type="cellIs" priority="2" operator="greaterThan">
-      <formula>"0.75"</formula>
+  <conditionalFormatting sqref="P2:P36">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="greaterThan">
       <formula>0.75</formula>
     </cfRule>
   </conditionalFormatting>
